--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:47</t>
+    <t xml:space="preserve">2026-09-10 00:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:57</t>
+    <t xml:space="preserve">2026-09-18 11:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:05</t>
+    <t xml:space="preserve">2026-09-23 14:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -700,7 +700,9 @@
       <c r="C13" s="2" t="n">
         <v>14204</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E13" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:27</t>
+    <t xml:space="preserve">2026-10-02 15:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2022_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2022_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:40</t>
+    <t xml:space="preserve">2026-10-05 14:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
